--- a/arkusz/obszar.xlsx
+++ b/arkusz/obszar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olek\Downloads\Factorial2\arkusz\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C58A78-17CE-4615-A294-05ECE908D616}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040FBC9F-A449-42A2-9B88-99DC0A4AFFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="375" yWindow="375" windowWidth="21000" windowHeight="11190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4004,7 +4004,7 @@
         <v>0.30000000000000054</v>
       </c>
       <c r="B39" s="11">
-        <f t="shared" ref="B39:B70" si="3">A39^2</f>
+        <f t="shared" ref="B39:B59" si="3">A39^2</f>
         <v>9.000000000000033E-2</v>
       </c>
       <c r="C39" s="11">
